--- a/data/trans_bre/P13_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P13_R-Edad-trans_bre.xlsx
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,54</t>
+          <t>-1,39; 2,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,5</t>
+          <t>-2,63; 1,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,87</t>
+          <t>0,32; 3,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,97</t>
+          <t>-1,31; 0,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 229,35</t>
+          <t>-47,26; 210,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,3; 115,14</t>
+          <t>-74,54; 110,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,7</t>
+          <t>-0,38; 2,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,77</t>
+          <t>-0,39; 3,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,27</t>
+          <t>-1,78; 1,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,62</t>
+          <t>-4,42; 1,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 381,74</t>
+          <t>-26,09; 409,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 256,94</t>
+          <t>-14,61; 242,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,61; 126,99</t>
+          <t>-66,9; 122,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,23; 73,73</t>
+          <t>-71,02; 77,32</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,38</t>
+          <t>-3,38; 1,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,12</t>
+          <t>0,09; 5,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,24</t>
+          <t>-2,76; 1,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,23</t>
+          <t>-2,99; 1,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 52,61</t>
+          <t>-60,5; 42,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 173,62</t>
+          <t>-3,24; 162,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-56,82; 55,1</t>
+          <t>-58,46; 65,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-55,65; 58,7</t>
+          <t>-57,29; 57,51</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,64</t>
+          <t>0,63; 4,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,29</t>
+          <t>1,55; 7,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,76</t>
+          <t>0,08; 4,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,24</t>
+          <t>-0,86; 4,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,83; 678,35</t>
+          <t>10,59; 620,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,76; 247,38</t>
+          <t>24,39; 222,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 165,77</t>
+          <t>-0,31; 172,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 240,95</t>
+          <t>-18,27; 257,67</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,85</t>
+          <t>-0,77; 5,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 9,22</t>
+          <t>2,42; 9,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,58</t>
+          <t>0,31; 6,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,15</t>
+          <t>-1,25; 3,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 244,56</t>
+          <t>-21,03; 261,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,34; 316,64</t>
+          <t>37,47; 340,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 242,54</t>
+          <t>4,31; 262,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 84,32</t>
+          <t>-15,5; 77,66</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,44</t>
+          <t>-1,4; 6,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,13; 13,02</t>
+          <t>2,69; 13,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 5,53</t>
+          <t>-1,17; 5,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 2,41</t>
+          <t>-5,98; 2,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 150,43</t>
+          <t>-19,41; 153,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,21; 214,74</t>
+          <t>21,7; 216,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 225,44</t>
+          <t>-25,74; 194,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,52; 36,82</t>
+          <t>-69,0; 38,25</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 8,68</t>
+          <t>-2,86; 8,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,37; 18,2</t>
+          <t>4,35; 17,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 11,5</t>
+          <t>0,98; 11,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 15,6</t>
+          <t>6,84; 15,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 124,18</t>
+          <t>-22,47; 136,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,13; 186,36</t>
+          <t>23,03; 169,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 169,4</t>
+          <t>6,28; 165,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,89; 137,77</t>
+          <t>41,0; 136,07</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,56</t>
+          <t>0,74; 2,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,89</t>
+          <t>3,34; 5,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,12</t>
+          <t>1,03; 3,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,3</t>
+          <t>0,57; 3,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,35; 93,65</t>
+          <t>18,12; 96,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,16; 146,34</t>
+          <t>63,41; 143,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,09; 103,33</t>
+          <t>25,67; 101,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,92; 83,86</t>
+          <t>11,1; 85,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P13_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P13_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-16,45%</t>
+          <t>-69,24%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,48</t>
+          <t>-1,41; 2,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,45</t>
+          <t>-2,45; 1,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,13</t>
+          <t>0,3; 2,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,76</t>
+          <t>-3,64; 0,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 210,22</t>
+          <t>-49,62; 224,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,54; 110,13</t>
+          <t>-70,84; 116,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-28,34%</t>
+          <t>-26,27%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,67</t>
+          <t>-0,21; 2,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,62</t>
+          <t>-0,23; 3,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,22</t>
+          <t>-1,84; 1,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,55</t>
+          <t>-4,21; 1,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 409,93</t>
+          <t>-22,44; 352,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 242,0</t>
+          <t>-15,06; 250,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,9; 122,4</t>
+          <t>-71,36; 118,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,02; 77,32</t>
+          <t>-65,68; 78,43</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-17,31%</t>
+          <t>-8,19%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,19</t>
+          <t>-3,26; 1,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,12</t>
+          <t>-0,15; 4,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,44</t>
+          <t>-2,75; 1,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,31</t>
+          <t>-2,09; 1,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,5; 42,32</t>
+          <t>-59,71; 43,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 162,66</t>
+          <t>-6,13; 152,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 65,24</t>
+          <t>-59,62; 65,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-57,29; 57,51</t>
+          <t>-49,86; 71,4</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,74</t>
+          <t>0,64; 4,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,28</t>
+          <t>1,25; 7,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,93</t>
+          <t>-0,44; 5,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,05</t>
+          <t>-1,45; 2,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 620,84</t>
+          <t>12,12; 621,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,39; 222,65</t>
+          <t>20,56; 238,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 172,41</t>
+          <t>-11,04; 160,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 257,67</t>
+          <t>-26,12; 91,14</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 5,13</t>
+          <t>-0,73; 4,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,37</t>
+          <t>2,26; 9,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,61</t>
+          <t>0,29; 6,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,94</t>
+          <t>-0,91; 4,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 261,69</t>
+          <t>-19,94; 233,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,47; 340,49</t>
+          <t>36,62; 317,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 262,82</t>
+          <t>2,5; 240,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 77,66</t>
+          <t>-12,05; 92,55</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-20,57%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 6,5</t>
+          <t>-1,78; 6,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 13,36</t>
+          <t>2,4; 13,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,3</t>
+          <t>-1,47; 5,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 2,41</t>
+          <t>-1,24; 4,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 153,11</t>
+          <t>-22,45; 148,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,7; 216,28</t>
+          <t>20,43; 207,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 194,47</t>
+          <t>-25,51; 215,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,0; 38,25</t>
+          <t>-14,01; 87,48</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,28</t>
+          <t>11,64</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 8,54</t>
+          <t>-3,48; 7,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 17,51</t>
+          <t>6,07; 18,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 11,2</t>
+          <t>0,91; 11,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 15,48</t>
+          <t>7,25; 16,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 136,51</t>
+          <t>-26,24; 111,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,03; 169,13</t>
+          <t>33,07; 183,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 165,28</t>
+          <t>7,48; 170,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>41,0; 136,07</t>
+          <t>44,75; 149,57</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,69</t>
+          <t>0,58; 2,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,95</t>
+          <t>3,53; 5,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,12</t>
+          <t>1,05; 3,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,37</t>
+          <t>1,12; 3,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,12; 96,14</t>
+          <t>15,73; 94,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,41; 143,83</t>
+          <t>68,32; 146,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,67; 101,19</t>
+          <t>26,24; 105,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,1; 85,35</t>
+          <t>19,21; 70,13</t>
         </is>
       </c>
     </row>
